--- a/Glossary.xlsx
+++ b/Glossary.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Grayson" sheetId="1" state="visible" r:id="rId3"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="10">
   <si>
     <t xml:space="preserve">Project Name</t>
   </si>
@@ -31,52 +31,28 @@
     <t xml:space="preserve">Description in 1-2 lines</t>
   </si>
   <si>
-    <t xml:space="preserve">Process setup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Process name</t>
+    <t xml:space="preserve">Process Names in order</t>
   </si>
   <si>
     <t xml:space="preserve">Process Parameters</t>
   </si>
   <si>
-    <t xml:space="preserve">Process Input</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Process Output</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information about input</t>
-  </si>
-  <si>
     <t xml:space="preserve">Input Material</t>
   </si>
   <si>
-    <t xml:space="preserve">Qualities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">String or Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Units</t>
-  </si>
-  <si>
-    <t xml:space="preserve">quality or realizable entity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devices used during, before or after process</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Device Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manufacturer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Standard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Serial Number</t>
+    <t xml:space="preserve">Qualities of material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Device Names</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Device Properties</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-process analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-process analzsis</t>
   </si>
 </sst>
 </file>
@@ -91,6 +67,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -112,6 +89,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -156,20 +134,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -296,125 +278,147 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:I19"/>
+  <dimension ref="B2:I41"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="21.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="21.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="23.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="21.37"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+    </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="2" t="s">
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="2"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="4"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="4"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="2" t="s">
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="3"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-    </row>
-    <row r="12" customFormat="false" ht="22.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="3" t="s">
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C28" s="3"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="2"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="2"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="0" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="33.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F19" s="0" t="s">
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -434,110 +438,136 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:F19"/>
+  <dimension ref="B2:F41"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16.48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="21.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="21.7"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+    </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="2"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="C17" s="3"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="4"/>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="4"/>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="2" t="s">
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="1"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-    </row>
-    <row r="12" customFormat="false" ht="22.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="3" t="s">
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C28" s="3"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="2"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="2"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="0" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="33.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F19" s="0" t="s">
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -557,110 +587,136 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:F19"/>
+  <dimension ref="B2:F41"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20.48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="21.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="21.37"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+    </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="2"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="C17" s="3"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="4"/>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="4"/>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="2" t="s">
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="1"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-    </row>
-    <row r="12" customFormat="false" ht="22.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="3" t="s">
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C28" s="3"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="2"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="2"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="0" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="33.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F19" s="0" t="s">
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -680,109 +736,137 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:F19"/>
+  <dimension ref="B2:F41"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="21.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="29.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.03"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+    </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="2"/>
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="2"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="C17" s="3"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="4"/>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="4"/>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="2" t="s">
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="1"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C28" s="3"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="2"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="2"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="0" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F19" s="0" t="s">
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="2" t="s">
         <v>9</v>
       </c>
     </row>
